--- a/docs/AI Models Credentials.xlsx
+++ b/docs/AI Models Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\break\Projects\TotalRecalls\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3468BF4C-90B3-436E-8528-4DDD17D67615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A860CA2A-11AE-42ED-8FD2-1F47A37D842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43395" yWindow="3495" windowWidth="9540" windowHeight="15555" xr2:uid="{7E254205-7D72-479A-B93B-5909398EDE61}"/>
   </bookViews>
@@ -83,7 +83,7 @@
     <t>breakwatercap.1@gmail.com</t>
   </si>
   <si>
-    <t>Bizard2024!!</t>
+    <t>Bizard2024!</t>
   </si>
 </sst>
 </file>
